--- a/MRB缺料.xlsx
+++ b/MRB缺料.xlsx
@@ -471,68 +471,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>物料编码</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>物料名称</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>工单缺料汇总</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>MRB库存数量</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>可覆盖缺口</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>处理进度</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>02.05.04885</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>钢托盘</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>-29</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>-16</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>暂无符合条件的数据</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -688,10 +634,10 @@
         <v>-18</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="7">

--- a/MRB缺料.xlsx
+++ b/MRB缺料.xlsx
@@ -471,28 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>暂无符合条件的数据</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -516,7 +495,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>待开缺料汇总</t>
+          <t>工单缺料汇总</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -538,6 +517,81 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
+          <t>02.05.04885</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>钢托盘</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>-29</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>-16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>物料编码</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>物料名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>待开缺料汇总</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>MRB库存数量</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>可覆盖缺口</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>处理进度</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
           <t>02.05.05545</t>
         </is>
       </c>
@@ -559,147 +613,126 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>15.05.00003</t>
+          <t>02.05.04885</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>子板组件</t>
+          <t>钢托盘</t>
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>-56</v>
+        <v>-40</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>-55</v>
+        <v>-27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>02.05.04885</t>
+          <t>04.09.02816</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>钢托盘</t>
+          <t>立柱通信线</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-40</v>
+        <v>-32</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-27</v>
+        <v>-31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>04.09.02816</t>
+          <t>04.03.00297</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>立柱通信线</t>
+          <t>黑白智能相机</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>-32</v>
+        <v>-18</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>-31</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>04.03.00297</t>
+          <t>10.12.00332</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>黑白智能相机</t>
+          <t>主控板PCBA-三防</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-18</v>
+        <v>-12</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-17</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>10.12.00332</t>
+          <t>04.03.00257</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>主控板PCBA-三防</t>
+          <t>黑白智能相机</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>04.03.00257</t>
+          <t>15.01.00012</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>黑白智能相机</t>
+          <t>主控组件</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>15.01.00012</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>主控组件</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>-9</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="6" t="n">
         <v>-6</v>
       </c>
     </row>

--- a/MRB缺料.xlsx
+++ b/MRB缺料.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -100,10 +100,16 @@
     <xf numFmtId="4" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -534,6 +540,7 @@
       <c r="E2" s="4" t="n">
         <v>-16</v>
       </c>
+      <c r="F2" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -604,32 +611,34 @@
         <v>-82</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>300</v>
+        <v>156</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>218</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>02.05.04885</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>钢托盘</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="7" t="n">
         <v>-40</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="7" t="n">
         <v>-27</v>
       </c>
+      <c r="F3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -651,27 +660,29 @@
       <c r="E4" s="4" t="n">
         <v>-31</v>
       </c>
+      <c r="F4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>04.03.00297</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>黑白智能相机</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <v>-18</v>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>-17</v>
-      </c>
+      <c r="D5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>-16</v>
+      </c>
+      <c r="F5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -693,27 +704,29 @@
       <c r="E6" s="4" t="n">
         <v>-11</v>
       </c>
+      <c r="F6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>04.03.00257</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>黑白智能相机</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <v>-11</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="7" t="n">
         <v>-10</v>
       </c>
+      <c r="F7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -735,6 +748,7 @@
       <c r="E8" s="4" t="n">
         <v>-6</v>
       </c>
+      <c r="F8" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
